--- a/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
+++ b/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>/gutter-cleaning/</t>
+          <t>/fascias-and-soffits/</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -740,15 +740,15 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Gutter Cleaning Manchester | Manchester Gutters</t>
+          <t>Fascias and Soffits Manchester | Manchester Gutters</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Gutter Cleaning Manchester</t>
+          <t>Fascias and Soffits Manchester</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>/fascias-and-soffits/</t>
+          <t>/downpipes/</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -804,15 +804,15 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Fascias and Soffits Manchester | Manchester Gutters</t>
+          <t>Downpipe Repairs Manchester | Manchester Gutters</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Fascias and Soffits Manchester</t>
+          <t>Downpipe Repairs Manchester</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>/downpipes/</t>
+          <t>/gutter-cleaning/</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -868,15 +868,15 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Downpipe Repairs Manchester | Manchester Gutters</t>
+          <t>Gutter Cleaning Manchester | Manchester Gutters</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Downpipe Repairs Manchester</t>
+          <t>Gutter Cleaning Manchester</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -904,7 +904,11 @@
           <t>Service, WebPage, Person, FAQPage, BreadcrumbList</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Offered but not a priority (low-ticket). One page; left out of the location ranking and of hub and town priorities</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -970,7 +974,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Secondary trade: build only if roofing is in scope; it then needs its own hub named for the search</t>
+          <t>Secondary trade. The site is gutter-led by choice: gutters are easier to compete for and gutter jobs lead on to roofing. One service page if roofing is in scope; no roofing hubs</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1040,11 @@
           <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>470 gutter searches a month</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1059,7 +1067,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1100,12 +1108,16 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>/guttering-manchester/chorlton/</t>
+          <t>/guttering-manchester/clayton/</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1123,20 +1135,20 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Guttering Chorlton, Manchester | Manchester Gutters</t>
+          <t>Guttering Clayton, Manchester | Manchester Gutters</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Guttering Chorlton, Manchester</t>
+          <t>Guttering Clayton, Manchester</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1164,21 +1176,25 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>/guttering-manchester/withington/</t>
+          <t>/guttering-stockport/</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -1187,53 +1203,57 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Guttering Withington, Manchester | Manchester Gutters</t>
+          <t>Guttering Stockport | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Guttering Withington, Manchester</t>
+          <t>Guttering Stockport</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,200-1,800</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>its hub; nearest in-hub siblings; articles about the place</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>160 gutter searches a month</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>/guttering-manchester/levenshulme/</t>
+          <t>/guttering-stockport/cheadle/</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1251,20 +1271,20 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Guttering Levenshulme, Manchester | Manchester Gutters</t>
+          <t>Guttering Cheadle, Stockport | Manchester Gutters</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Guttering Levenshulme, Manchester</t>
+          <t>Guttering Cheadle, Stockport</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1292,12 +1312,16 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 90 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>/guttering-manchester/sale/</t>
+          <t>/guttering-stockport/bramhall/</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1315,20 +1339,20 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Guttering Sale, Manchester | Manchester Gutters</t>
+          <t>Guttering Bramhall, Stockport | Manchester Gutters</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Guttering Sale, Manchester</t>
+          <t>Guttering Bramhall, Stockport</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1356,12 +1380,16 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 50 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>/guttering-manchester/altrincham/</t>
+          <t>/guttering-stockport/cheadle-hulme/</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1379,20 +1407,20 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Guttering Altrincham, Manchester | Manchester Gutters</t>
+          <t>Guttering Cheadle Hulme, Stockport | Manchester Gutters</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Guttering Altrincham, Manchester</t>
+          <t>Guttering Cheadle Hulme, Stockport</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1420,12 +1448,16 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 40 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>/guttering-manchester/stretford/</t>
+          <t>/guttering-stockport/marple/</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1443,20 +1475,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Guttering Stretford, Manchester | Manchester Gutters</t>
+          <t>Guttering Marple, Stockport | Manchester Gutters</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Guttering Stretford, Manchester</t>
+          <t>Guttering Marple, Stockport</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1484,21 +1516,25 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 40 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>/guttering-salford/</t>
+          <t>/guttering-stockport/davenport/</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Area hub</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1507,62 +1543,66 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Guttering Salford | Repairs, Prices | Manchester Gutters</t>
+          <t>Guttering Davenport, Stockport | Manchester Gutters</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Guttering Salford</t>
+          <t>Guttering Davenport, Stockport</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,500-5,000</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>home; its towns; other hubs; articles about the place</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>every service; every town under it; other hubs; guide cards</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>/guttering-salford/eccles/</t>
+          <t>/guttering-oldham/</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1571,53 +1611,57 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Guttering Eccles, Salford | Manchester Gutters</t>
+          <t>Guttering Oldham | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Guttering Eccles, Salford</t>
+          <t>Guttering Oldham</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,200-1,800</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>its hub; nearest in-hub siblings; articles about the place</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>150 gutter searches a month</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>/guttering-salford/swinton/</t>
+          <t>/guttering-oldham/chadderton/</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1635,20 +1679,20 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Guttering Swinton, Salford | Manchester Gutters</t>
+          <t>Guttering Chadderton, Oldham | Manchester Gutters</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Guttering Swinton, Salford</t>
+          <t>Guttering Chadderton, Oldham</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1676,21 +1720,25 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>/guttering-salford/worsley/</t>
+          <t>/guttering-wigan/</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1699,62 +1747,66 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Guttering Worsley, Salford | Manchester Gutters</t>
+          <t>Guttering Wigan | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Guttering Worsley, Salford</t>
+          <t>Guttering Wigan</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,200-1,800</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>its hub; nearest in-hub siblings; articles about the place</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>130 gutter searches a month</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>/guttering-stockport/</t>
+          <t>/guttering-wigan/leigh/</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Area hub</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -1763,53 +1815,57 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Guttering Stockport | Repairs, Prices | Manchester Gutters</t>
+          <t>Guttering Leigh, Wigan | Manchester Gutters</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Guttering Stockport</t>
+          <t>Guttering Leigh, Wigan</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,500-5,000</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>home; its towns; other hubs; articles about the place</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>every service; every town under it; other hubs; guide cards</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 100 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>/guttering-stockport/bramhall/</t>
+          <t>/guttering-wigan/atherton/</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1827,20 +1883,20 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Guttering Bramhall, Stockport | Manchester Gutters</t>
+          <t>Guttering Atherton, Wigan | Manchester Gutters</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Guttering Bramhall, Stockport</t>
+          <t>Guttering Atherton, Wigan</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1868,12 +1924,16 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>/guttering-stockport/cheadle/</t>
+          <t>/guttering-wigan/standish/</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1891,20 +1951,20 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Guttering Cheadle, Stockport | Manchester Gutters</t>
+          <t>Guttering Standish, Wigan | Manchester Gutters</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Guttering Cheadle, Stockport</t>
+          <t>Guttering Standish, Wigan</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1932,21 +1992,25 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>/guttering-stockport/marple/</t>
+          <t>/guttering-bolton/</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -1955,62 +2019,66 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Guttering Marple, Stockport | Manchester Gutters</t>
+          <t>Guttering Bolton | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Guttering Marple, Stockport</t>
+          <t>Guttering Bolton</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,200-1,800</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>its hub; nearest in-hub siblings; articles about the place</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>120 gutter searches a month</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>/guttering-bolton/</t>
+          <t>/guttering-bolton/westhoughton/</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Area hub</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -2019,48 +2087,52 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Guttering Bolton | Repairs, Prices | Manchester Gutters</t>
+          <t>Guttering Westhoughton, Bolton | Manchester Gutters</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Guttering Bolton</t>
+          <t>Guttering Westhoughton, Bolton</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,500-5,000</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>home; its towns; other hubs; articles about the place</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>every service; every town under it; other hubs; guide cards</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2083,7 +2155,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2124,21 +2196,25 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>/guttering-bolton/farnworth/</t>
+          <t>/guttering-bury/</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -2147,53 +2223,57 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Guttering Farnworth, Bolton | Manchester Gutters</t>
+          <t>Guttering Bury | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Guttering Farnworth, Bolton</t>
+          <t>Guttering Bury</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,200-1,800</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>its hub; nearest in-hub siblings; articles about the place</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>70 gutter searches a month</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>/guttering-bolton/westhoughton/</t>
+          <t>/guttering-bury/prestwich/</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2211,20 +2291,20 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>With a place brief</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Guttering Westhoughton, Bolton | Manchester Gutters</t>
+          <t>Guttering Prestwich, Bury | Manchester Gutters</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Guttering Westhoughton, Bolton</t>
+          <t>Guttering Prestwich, Bury</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2252,17 +2332,21 @@
           <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 60 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>/gutter-replacement/stockport/</t>
+          <t>/guttering-bury/ramsbottom/</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Service in place</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2275,66 +2359,66 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Only with data</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Gutter Replacement Stockport | Manchester Gutters</t>
+          <t>Guttering Ramsbottom, Bury | Manchester Gutters</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Gutter Replacement Stockport</t>
+          <t>Guttering Ramsbottom, Bury</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,200-2,200</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Mirror of the hub for one service</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>its service; sibling cities</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>up to the service; sibling cities; areas as text</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Service (areaServed), WebPage, BreadcrumbList, FAQPage</t>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Built only when Search Console shows "&lt;service&gt; &lt;place&gt;" impressions with no page named for them</t>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-repair-cost/</t>
+          <t>/guttering-rochdale/</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Article: pillar</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
@@ -2343,58 +2427,62 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>With demand evidence</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>How Much Do Gutter Repairs Cost? | Manchester Gutters</t>
+          <t>Guttering Rochdale | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>How Much Do Gutter Repairs Cost?</t>
+          <t>Guttering Rochdale</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,000-1,800</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>blog index; hub guide cards; pillar/spokes</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>BlogPosting, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>60 gutter searches a month</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-repair-cost-manchester/</t>
+          <t>/guttering-rochdale/middleton/</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Article: spoke</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2407,58 +2495,62 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>With demand evidence</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Gutter Repair Cost in Manchester | Manchester Gutters</t>
+          <t>Guttering Middleton, Rochdale | Manchester Gutters</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Gutter Repair Cost in Manchester</t>
+          <t>Guttering Middleton, Rochdale</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,000-1,800</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>blog index; hub guide cards; pillar/spokes</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>BlogPosting, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 50 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-cleaning-cost-stockport/</t>
+          <t>/guttering-rochdale/littleborough/</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Article: spoke</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2471,12 +2563,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>With demand evidence</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Gutter Cleaning Cost in Stockport | Manchester Gutters</t>
+          <t>Guttering Littleborough, Rochdale | Manchester Gutters</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -2484,49 +2576,53 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Gutter Cleaning Cost in Stockport</t>
+          <t>Guttering Littleborough, Rochdale</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,000-1,800</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>blog index; hub guide cards; pillar/spokes</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>BlogPosting, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/guttering-rochdale/langley/</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Blog index</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
@@ -2535,58 +2631,62 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>When articles exist</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Guttering Guides and Costs | Manchester Gutters</t>
+          <t>Guttering Langley, Rochdale | Manchester Gutters</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Guttering guides</t>
+          <t>Guttering Langley, Rochdale</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>200-400</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Groups by topic; 20 cards then pages</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>nav</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>every article</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>CollectionPage, BreadcrumbList</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>/reviews/</t>
+          <t>/guttering-salford/</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2599,62 +2699,66 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>Guttering Salford | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>Guttering Salford</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>10 gutter searches a month; kept as the parent of its towns, no gutter demand under its own name</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>/case-studies/</t>
+          <t>/guttering-salford/swinton/</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
@@ -2663,62 +2767,66 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Case Studies | Manchester Gutters</t>
+          <t>Guttering Swinton, Salford | Manchester Gutters</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Case Studies</t>
+          <t>Guttering Swinton, Salford</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 40 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>/price-guide/</t>
+          <t>/guttering-salford/eccles/</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
@@ -2727,58 +2835,62 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide | Manchester Gutters</t>
+          <t>Guttering Eccles, Salford | Manchester Gutters</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide</t>
+          <t>Guttering Eccles, Salford</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>/gallery/</t>
+          <t>/guttering-tameside/</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Area hub</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2791,62 +2903,66 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs | Manchester Gutters</t>
+          <t>Guttering Tameside | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs</t>
+          <t>Guttering Tameside</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>10 gutter searches a month; kept as the parent of its towns, no gutter demand under its own name</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>/about/</t>
+          <t>/guttering-tameside/denton/</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
@@ -2855,12 +2971,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters | Local Guttering Team</t>
+          <t>Guttering Denton, Tameside | Manchester Gutters</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
@@ -2868,49 +2984,53 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters</t>
+          <t>Guttering Denton, Tameside</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>600-1,200</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Named people, credentials table, contact by area, map after consent</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>AboutPage / ContactPage + Organization reference</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 100 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>/contact/</t>
+          <t>/guttering-tameside/ashton-under-lyne/</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -2919,62 +3039,66 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
+          <t>Guttering Ashton-under-Lyne, Tameside | Manchester Gutters</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters</t>
+          <t>Guttering Ashton-under-Lyne, Tameside</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>600-1,200</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Named people, credentials table, contact by area, map after consent</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>AboutPage / ContactPage + Organization reference</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 50 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>/privacy-policy/</t>
+          <t>/guttering-tameside/hyde/</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
@@ -2983,62 +3107,66 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy | Manchester Gutters</t>
+          <t>Guttering Hyde, Tameside | Manchester Gutters</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy</t>
+          <t>Guttering Hyde, Tameside</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>as needed</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>What the site really does</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>WebPage</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>/cookie-policy/</t>
+          <t>/guttering-tameside/stalybridge/</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
@@ -3047,68 +3175,70 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Wave 2, with a place brief</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Cookie Policy | Manchester Gutters</t>
+          <t>Guttering Stalybridge, Tameside | Manchester Gutters</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Guttering Stalybridge, Tameside</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>as needed</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>What the site really does</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>WebPage</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>/404</t>
+          <t>/guttering-trafford/</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Area hub</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3118,260 +3248,1506 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering Trafford | Repairs, Prices | Manchester Gutters</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering Trafford</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2,500-5,000</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Hero; credentials + logos; at a glance; what you need to know + office + form; town cards; services + problems we fix; costs table; projects/reviews/videos if records; why us; guide cards; FAQ 8-12; other hubs; CTA + form</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>home; its towns; other hubs; articles about the place</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>every service; every town under it; other hubs; guide cards</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>WebPage, Service (areaServed), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>served with HTTP status 404</t>
+          <t>0 gutter searches a month; kept as the parent of its towns, no gutter demand under its own name</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>/sitemap.xml</t>
+          <t>/guttering-trafford/altrincham/</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering Altrincham, Trafford | Manchester Gutters</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering Altrincham, Trafford</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>indexable pages only; real lastmod dates</t>
+          <t>Launch: 530 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>/robots.txt</t>
+          <t>/guttering-trafford/sale/</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, with a place brief</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering Sale, Trafford | Manchester Gutters</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering Sale, Trafford</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>1,200-1,800</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>allows the AI search crawlers; points to the sitemap</t>
+          <t>Launch: 330 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>/guttering-trafford/urmston/</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Launch, with a place brief</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Urmston, Trafford | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Urmston, Trafford</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>1,200-1,800</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Launch: 80 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>/guttering-trafford/hale/</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2, with a place brief</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Hale, Trafford | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Hale, Trafford</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>1,200-1,800</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 30 roofing searches a month (no gutter volume below hub level; roofing is the proxy); name also used elsewhere in the UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>/guttering-trafford/stretford/</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2, with a place brief</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Stretford, Trafford | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Stretford, Trafford</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>1,200-1,800</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Hero + breadcrumb; credentials; at a glance; local team + map; {Town} weather (3 H3); property types (3-4 H3); services grid; costings table; work in town if records; FAQ 6-8; nearby areas; CTA + form</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>its hub; nearest in-hub siblings; articles about the place</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>every service; its hub; 10-30 nearest siblings; proof (1 in prose)</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>WebPage, Service (areaServed = town), Person, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2: 20 roofing searches a month (no gutter volume below hub level; roofing is the proxy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>/gutter-repairs/stockport/</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Service in place</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Only with data</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Gutter Repairs Stockport | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Gutter Repairs Stockport</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>1,200-2,200</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Mirror of the hub for one service</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>its service; sibling cities</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>up to the service; sibling cities; areas as text</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Service (areaServed), WebPage, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Built only when Search Console shows "&lt;service&gt; &lt;place&gt;" impressions with no page named for them ("gutter repairs stockport": 110 a month in Keyword Planner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>/blog/gutter-repair-cost/</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Article: pillar</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>With demand evidence</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>How Much Do Gutter Repairs Cost? | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>How Much Do Gutter Repairs Cost?</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>1,000-1,800</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>blog index; hub guide cards; pillar/spokes</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>/blog/gutter-repair-cost-manchester/</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Article: spoke</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>With demand evidence</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Gutter Repair Cost in Manchester | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Gutter Repair Cost in Manchester</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>1,000-1,800</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>blog index; hub guide cards; pillar/spokes</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>/blog/gutter-replacement-cost-stockport/</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Article: spoke</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>With demand evidence</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Gutter Replacement Cost in Stockport | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Gutter Replacement Cost in Stockport</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>1,000-1,800</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>blog index; hub guide cards; pillar/spokes</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>/blog/</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Blog index</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>When articles exist</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Guides and Costs | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Guttering guides</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>200-400</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Groups by topic; 20 cards then pages</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>nav</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>every article</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>CollectionPage, BreadcrumbList</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>/reviews/</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Manchester Gutters Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Manchester Gutters Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>/case-studies/</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Case Studies | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>/price-guide/</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Price Guide | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Price Guide</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>/gallery/</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Gallery of Recent Jobs | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Gallery of Recent Jobs</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>/about/</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>About Manchester Gutters | Local Guttering Team</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>About Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>600-1,200</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Named people, credentials table, contact by area, map after consent</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>AboutPage / ContactPage + Organization reference</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>/contact/</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Contact Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>600-1,200</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Named people, credentials table, contact by area, map after consent</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>AboutPage / ContactPage + Organization reference</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>/privacy-policy/</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Privacy Policy | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>as needed</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>What the site really does</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>WebPage</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>/cookie-policy/</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Cookie Policy | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Cookie Policy</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>as needed</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>What the site really does</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>WebPage</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>/404</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>served with HTTP status 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>/sitemap.xml</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>indexable pages only; real lastmod dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>/robots.txt</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>allows the AI search crawlers; points to the sitemap</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
           <t>/llms.txt</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Utility</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Non-indexable</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Launch</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>public facts only, from the facts file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N45"/>
+  <autoFilter ref="A1:N64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3382,7 +4758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -3398,26 +4774,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Illustrative. Services, hubs and towns are confirmed by demand research (search volumes, top-10 overlap) and the client brief before anything is built.</t>
+          <t>Hubs and towns: from the location research ranking (Keyword Planner, UK, October 2026; manchester-gutters-location-research.xlsx). Hubs = the ten Greater Manchester boroughs; towns = Launch and Wave 2 rows. Hold towns stay in the ranking sheet.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trade phrase in hub URLs is "guttering" pending the central-search-intent check; it may become "gutter-repairs" or "gutters".</t>
+          <t>Gutter-led by choice (Andrew, 25 October 2026). Gutter cleaning is offered but not a priority. Services and proof pages are confirmed by the client brief before anything is built.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Columns follow a Screaming Frog Internal: HTML export so the plan can be compared with a crawl of the built site.</t>
+          <t>Trade phrase in hub URLs is "guttering" pending the central-search-intent check; it may become "gutter-repairs" or "gutters".</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>Columns follow a Screaming Frog Internal: HTML export so the plan can be compared with a crawl of the built site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Build stage: Launch = in the first release; With a place brief / With demand evidence / When records exist = added only when that condition is met.</t>
         </is>

--- a/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
+++ b/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3701,7 +3701,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-repair-cost/</t>
+          <t>/blog/gutter-replacement-cost/</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3719,20 +3719,20 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>With demand evidence</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>How Much Do Gutter Repairs Cost? | Manchester Gutters</t>
+          <t>How Much Does Gutter Replacement Cost? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>How Much Do Gutter Repairs Cost?</t>
+          <t>How Much Does Gutter Replacement Cost?</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3742,17 +3742,17 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); three cost tables (by property type, additional costs, lifespan) from the client's records; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>blog index; hub guide cards; pillar/spokes</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3760,17 +3760,21 @@
           <t>BlogPosting, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>3,640 UK searches a month across 21 searches (gutter replacement cost 1300; how much to replace guttering 390; new gutters price 320; how much do gutters cost 170). Folded in as sections: how long does guttering last, guttering building regulations, are gutter guards worth it, gutter guards cost. Sister site: Munster "how much to replace gutters" (234 impressions, position 5). Overlap test against /gutter-replacement/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-repair-cost-manchester/</t>
+          <t>/blog/fascia-and-soffit-replacement-cost/</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Article: spoke</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3783,20 +3787,20 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>With demand evidence</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Gutter Repair Cost in Manchester | Manchester Gutters</t>
+          <t>Fascia and Soffit Replacement Cost | Manchester Gutters</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Gutter Repair Cost in Manchester</t>
+          <t>Fascia and Soffit Replacement Cost</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3806,17 +3810,17 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); three cost tables (by property type, additional costs, lifespan) from the client's records; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>blog index; hub guide cards; pillar/spokes</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3824,17 +3828,21 @@
           <t>BlogPosting, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>1,850 UK searches a month across 13 searches (cost of fascia and soffit replacement 590; soffit and fascia prices 390; fascia replacement cost 210; fascia board replacement cost 210). Folded in as sections: fascia capping vs replacement. Sister site: Munster fascia and soffit cost article: 57 clicks. Overlap test against /fascias-and-soffits/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-replacement-cost-stockport/</t>
+          <t>/blog/roofline-replacement-cost/</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Article: spoke</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3847,20 +3855,20 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>With demand evidence</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Gutter Replacement Cost in Stockport | Manchester Gutters</t>
+          <t>Cost of New Gutters, Fascias and Soffits</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Gutter Replacement Cost in Stockport</t>
+          <t>Cost of New Gutters, Fascias and Soffits</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3870,17 +3878,17 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; Read next; question H2s (60%+) with cost list, chart and comparison table; case/review/video if records; who to hire; guarantees; nearby areas; FAQ 10-12; related cards; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); three cost tables (by property type, additional costs, lifespan) from the client's records; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>blog index; hub guide cards; pillar/spokes</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>services (3-5 in prose); the place hub and town; pillar once; Read next 3-4</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3888,21 +3896,25 @@
           <t>BlogPosting, BreadcrumbList, FAQPage</t>
         </is>
       </c>
-      <c r="N51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>960 UK searches a month across 10 searches (gutter fascia and soffit replacement cost 320; gutter and fascia replacement cost 320; fascias and guttering cost 70; new gutter and fascia cost 50). Overlap test against /fascias-and-soffits/ and /gutter-replacement/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/blog/gutter-repair-cost/</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Blog index</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
@@ -3911,62 +3923,66 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>When articles exist</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Guttering Guides and Costs | Manchester Gutters</t>
+          <t>How Much Do Gutter Repairs Cost? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Guttering guides</t>
+          <t>How Much Do Gutter Repairs Cost?</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>200-400</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Groups by topic; 20 cards then pages</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); three cost tables (by property type, additional costs, lifespan) from the client's records; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>nav</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>every article</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>CollectionPage, BreadcrumbList</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>640 UK searches a month across 8 searches (gutter repair cost 390; gutter leak repair cost 90; how much to repair gutters 50; leaking gutter repair cost 30). Sister site: Munster "Average cost of gutter repairs": 33 clicks. Overlap test against /gutter-repairs/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>/reviews/</t>
+          <t>/blog/concrete-finlock-gutters/</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
@@ -3975,62 +3991,66 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>Concrete Finlock Gutters, Repair or Replace</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>Concrete Finlock Gutters, Repair or Replace</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); three cost tables (by property type, additional costs, lifespan) from the client's records; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>240 UK searches a month across 4 searches (concrete gutter replacement cost 70; concrete gutter repair 70; finlock gutter removal cost 50; finlock gutter repair 50). Overlap test against /gutter-replacement/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>/case-studies/</t>
+          <t>/blog/leaking-gutter-joint/</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -4039,62 +4059,66 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Case Studies | Manchester Gutters</t>
+          <t>How to Fix a Leaking Gutter Joint | Manchester Gutters</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Case Studies</t>
+          <t>How to Fix a Leaking Gutter Joint</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>2,100 UK searches a month across 10 searches (gutter leaking at joint 1000; sealing gutter joints 390; how to fix a leaking gutter joint 260; fix leaking gutter joint 170). Overlap test against /gutter-repairs/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>/price-guide/</t>
+          <t>/blog/why-is-my-gutter-leaking/</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
@@ -4103,12 +4127,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide | Manchester Gutters</t>
+          <t>Why Is My Gutter Leaking and How to Fix It</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
@@ -4116,49 +4140,53 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide</t>
+          <t>Why Is My Gutter Leaking and How to Fix It</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>1,520 UK searches a month across 10 searches (gutter leaking 480; gutter leak repairs 480; how to fix a leaking gutter 210; sealing gutter leaks 140). Overlap test against /gutter-repairs/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>/gallery/</t>
+          <t>/blog/blocked-downpipe/</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
@@ -4167,62 +4195,66 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs | Manchester Gutters</t>
+          <t>Blocked or Leaking Downpipe? What to Do | Manchester Gutters</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs</t>
+          <t>Blocked or Leaking Downpipe? What to Do</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>460 UK searches a month across 3 searches (downpipe blocked 260; how to unblock a downpipe 110; downpipe leaking 90). Overlap test against /downpipes/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>/about/</t>
+          <t>/blog/rotten-fascia-boards/</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
@@ -4231,62 +4263,66 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters | Local Guttering Team</t>
+          <t>Rotten Fascia Boards, Repair or Replace?</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters</t>
+          <t>Rotten Fascia Boards, Repair or Replace?</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>600-1,200</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Named people, credentials table, contact by area, map after consent</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>AboutPage / ContactPage + Organization reference</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>420 UK searches a month across 4 searches (fixing soffits and fascias 170; how to fit fascia boards 140; rotten fascia boards 70; how to replace soffits 40). Folded in as sections: signs fascia needs replacing. Overlap test against /fascias-and-soffits/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>/contact/</t>
+          <t>/blog/gutters-overflowing/</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
@@ -4295,62 +4331,66 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
+          <t>Why Are My Gutters Overflowing? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters</t>
+          <t>Why Are My Gutters Overflowing?</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>600-1,200</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Named people, credentials table, contact by area, map after consent</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>AboutPage / ContactPage + Organization reference</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>340 UK searches a month across 3 searches (gutters overflowing 260; gutter overflowing in heavy rain 70; why are my gutters overflowing 10). Overlap test against /gutter-repairs/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>/privacy-policy/</t>
+          <t>/blog/box-gutter-leaking/</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
@@ -4359,62 +4399,66 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy | Manchester Gutters</t>
+          <t>Leaking Box Gutters and Conservatory Gutters</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy</t>
+          <t>Leaking Box Gutters and Conservatory Gutters</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>as needed</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>What the site really does</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>WebPage</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>240 UK searches a month across 3 searches (conservatory box gutter leaking 140; fixing box gutters 70; box gutter leaking 30). Overlap test against /gutter-repairs/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>/cookie-policy/</t>
+          <t>/blog/how-to-replace-guttering/</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
@@ -4423,208 +4467,206 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Cookie Policy | Manchester Gutters</t>
+          <t>How to Replace Guttering Step by Step | Manchester Gutters</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>How to Replace Guttering Step by Step</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>as needed</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>What the site really does</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>WebPage</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>1,140 UK searches a month across 8 searches (how to replace guttering 480; how to fit guttering 210; how to fix guttering 170; how to cut guttering 170). Folded in as sections: tools for fitting guttering, gutter installation mistakes. Sister site: Munster step-by-step installation guide: 68 clicks. Overlap test against /gutter-replacement/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>/404</t>
+          <t>/blog/gutter-fall-and-bracket-spacing/</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Article: pillar</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Gutter Fall and Bracket Spacing Explained</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Gutter Fall and Bracket Spacing Explained</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>served with HTTP status 404</t>
+          <t>840 UK searches a month across 5 searches (fall for guttering 480; guttering fall per metre 140; how far apart should gutter brackets be 110; how many gutter brackets per meter 70). Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>/sitemap.xml</t>
+          <t>/blog/rogue-roofers/</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Article: pillar</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>How to Spot a Rogue Roofer and Hire Safely</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>How to Spot a Rogue Roofer and Hire Safely</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>indexable pages only; real lastmod dates</t>
+          <t>280 UK searches a month across 6 searches (roofing scams 90; cowboy roofers 90; rogue roofers 40; roofing scams uk 30). Folded in as sections: how to complain about a builder. Sister site: Munster "Irish roofer scams": 72 clicks</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>/robots.txt</t>
+          <t>/blog/</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Blog index</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4634,120 +4676,838 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering Guides and Costs | Manchester Gutters</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Guttering guides</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>200-400</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Groups by topic; 20 cards then pages</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>nav</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>every article</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>allows the AI search crawlers; points to the sitemap</t>
-        </is>
-      </c>
+          <t>CollectionPage, BreadcrumbList</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>/reviews/</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Manchester Gutters Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Manchester Gutters Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>/case-studies/</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Case Studies | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>/price-guide/</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Price Guide | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Guttering Price Guide</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>/gallery/</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>When records exist</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Gallery of Recent Jobs | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Gallery of Recent Jobs</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>as records allow</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer; towns and services (1 in prose)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>issuers (Google profile, memberships)</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>/about/</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>About Manchester Gutters | Local Guttering Team</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>About Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>600-1,200</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Named people, credentials table, contact by area, map after consent</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>AboutPage / ContactPage + Organization reference</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>/contact/</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Contact Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>600-1,200</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Named people, credentials table, contact by area, map after consent</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>AboutPage / ContactPage + Organization reference</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>/privacy-policy/</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Privacy Policy | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>as needed</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>What the site really does</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>WebPage</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>/cookie-policy/</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Indexable</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Cookie Policy | Manchester Gutters</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Cookie Policy</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>as needed</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>What the site really does</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>nav; footer</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>nav only</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>WebPage</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>/404</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>served with HTTP status 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>/sitemap.xml</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>indexable pages only; real lastmod dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>/robots.txt</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>allows the AI search crawlers; points to the sitemap</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>/llms.txt</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Utility</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Non-indexable</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Launch</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>public facts only, from the facts file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N64"/>
+  <autoFilter ref="A1:N75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
+++ b/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,640 UK searches a month across 21 searches (gutter replacement cost 1300; how much to replace guttering 390; new gutters price 320; how much do gutters cost 170). Folded in as sections: how long does guttering last, guttering building regulations, are gutter guards worth it, gutter guards cost. Sister site: Munster "how much to replace gutters" (234 impressions, position 5). Overlap test against /gutter-replacement/ before writing</t>
+          <t>4,270 UK searches a month across 35 searches (gutter replacement cost 1300; how much to replace guttering 390; new gutters price 320; how much do gutters cost 170). Folded in as sections: how long does guttering last, guttering building regulations. Sister site: Munster "how much to replace gutters" (234 impressions, position 5). Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>1,850 UK searches a month across 13 searches (cost of fascia and soffit replacement 590; soffit and fascia prices 390; fascia replacement cost 210; fascia board replacement cost 210). Folded in as sections: fascia capping vs replacement. Sister site: Munster fascia and soffit cost article: 57 clicks. Overlap test against /fascias-and-soffits/ before writing</t>
+          <t>2,590 UK searches a month across 28 searches (cost of fascia and soffit replacement 590; soffit and fascia prices 390; fascia replacement cost 210; fascia board replacement cost 210). Folded in as sections: fascia capping vs replacement. Sister site: Munster fascia and soffit cost article: 57 clicks. Overlap test against /fascias-and-soffits/ before writing</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>640 UK searches a month across 8 searches (gutter repair cost 390; gutter leak repair cost 90; how much to repair gutters 50; leaking gutter repair cost 30). Sister site: Munster "Average cost of gutter repairs": 33 clicks. Overlap test against /gutter-repairs/ before writing</t>
+          <t>640 UK searches a month across 9 searches (gutter repair cost 390; gutter leak repair cost 90; how much to repair gutters 50; leaking gutter repair cost 30). Sister site: Munster "Average cost of gutter repairs": 33 clicks. Overlap test against /gutter-repairs/ before writing</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>/blog/leaking-gutter-joint/</t>
+          <t>/blog/what-are-fascias-and-soffits/</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4064,15 +4064,15 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>How to Fix a Leaking Gutter Joint | Manchester Gutters</t>
+          <t>What Are Fascias and Soffits on a House?</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>How to Fix a Leaking Gutter Joint</t>
+          <t>What Are Fascias and Soffits on a House?</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -4102,14 +4102,14 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2,100 UK searches a month across 10 searches (gutter leaking at joint 1000; sealing gutter joints 390; how to fix a leaking gutter joint 260; fix leaking gutter joint 170). Overlap test against /gutter-repairs/ before writing</t>
+          <t>4,120 UK searches a month across 19 searches (what are soffits and fascias 1300; what are fascias on a house 590; fascia vs soffit 320; what are soffits on a house 320). Overlap test against /fascias-and-soffits/ before writing</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>/blog/why-is-my-gutter-leaking/</t>
+          <t>/blog/leaking-gutter-joint/</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -4132,15 +4132,15 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Why Is My Gutter Leaking and How to Fix It</t>
+          <t>How to Fix a Leaking Gutter Joint | Manchester Gutters</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Why Is My Gutter Leaking and How to Fix It</t>
+          <t>How to Fix a Leaking Gutter Joint</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>1,520 UK searches a month across 10 searches (gutter leaking 480; gutter leak repairs 480; how to fix a leaking gutter 210; sealing gutter leaks 140). Overlap test against /gutter-repairs/ before writing</t>
+          <t>2,410 UK searches a month across 16 searches (gutter leaking at joint 1000; sealing gutter joints 390; how to fix a leaking gutter joint 260; fix leaking gutter joint 170). Overlap test against /gutter-repairs/ before writing</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>/blog/blocked-downpipe/</t>
+          <t>/blog/why-is-my-gutter-leaking/</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4200,15 +4200,15 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Blocked or Leaking Downpipe? What to Do | Manchester Gutters</t>
+          <t>Why Is My Gutter Leaking and How to Fix It</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Blocked or Leaking Downpipe? What to Do</t>
+          <t>Why Is My Gutter Leaking and How to Fix It</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>460 UK searches a month across 3 searches (downpipe blocked 260; how to unblock a downpipe 110; downpipe leaking 90). Overlap test against /downpipes/ before writing</t>
+          <t>1,600 UK searches a month across 13 searches (gutter leaking 480; gutter leak repairs 480; how to fix a leaking gutter 210; sealing gutter leaks 140). Overlap test against /gutter-repairs/ before writing</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>/blog/rotten-fascia-boards/</t>
+          <t>/blog/blocked-downpipe/</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4268,15 +4268,15 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Rotten Fascia Boards, Repair or Replace?</t>
+          <t>Blocked or Leaking Downpipe? What to Do | Manchester Gutters</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Rotten Fascia Boards, Repair or Replace?</t>
+          <t>Blocked or Leaking Downpipe? What to Do</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4306,14 +4306,14 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>420 UK searches a month across 4 searches (fixing soffits and fascias 170; how to fit fascia boards 140; rotten fascia boards 70; how to replace soffits 40). Folded in as sections: signs fascia needs replacing. Overlap test against /fascias-and-soffits/ before writing</t>
+          <t>990 UK searches a month across 11 searches (downpipe blocked 260; blocked downpipe from gutter 210; how to unblock a downpipe 110; downpipe leaking 90). Overlap test against /downpipes/ before writing</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutters-overflowing/</t>
+          <t>/blog/rotten-fascia-boards/</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4336,15 +4336,15 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Why Are My Gutters Overflowing? | Manchester Gutters</t>
+          <t>Rotten Fascia Boards, Repair or Replace?</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Why Are My Gutters Overflowing?</t>
+          <t>Rotten Fascia Boards, Repair or Replace?</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>340 UK searches a month across 3 searches (gutters overflowing 260; gutter overflowing in heavy rain 70; why are my gutters overflowing 10). Overlap test against /gutter-repairs/ before writing</t>
+          <t>980 UK searches a month across 14 searches (fixing soffits and fascias 170; how to fit fascia boards 140; how to replace fascia and soffit 110; how to install fascia boards 90). Folded in as sections: signs fascia needs replacing. Overlap test against /fascias-and-soffits/ before writing</t>
         </is>
       </c>
     </row>
@@ -4442,14 +4442,14 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>240 UK searches a month across 3 searches (conservatory box gutter leaking 140; fixing box gutters 70; box gutter leaking 30). Overlap test against /gutter-repairs/ before writing</t>
+          <t>380 UK searches a month across 5 searches (conservatory box gutter leaking 140; what are box gutters 90; fixing box gutters 70; box gutter sizes 50). Overlap test against /gutter-repairs/ before writing</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>/blog/how-to-replace-guttering/</t>
+          <t>/blog/gutters-overflowing/</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4472,15 +4472,15 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>How to Replace Guttering Step by Step | Manchester Gutters</t>
+          <t>Why Are My Gutters Overflowing? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>How to Replace Guttering Step by Step</t>
+          <t>Why Are My Gutters Overflowing?</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>1,140 UK searches a month across 8 searches (how to replace guttering 480; how to fit guttering 210; how to fix guttering 170; how to cut guttering 170). Folded in as sections: tools for fitting guttering, gutter installation mistakes. Sister site: Munster step-by-step installation guide: 68 clicks. Overlap test against /gutter-replacement/ before writing</t>
+          <t>340 UK searches a month across 3 searches (gutters overflowing 260; gutter overflowing in heavy rain 70; why are my gutters overflowing 10). Overlap test against /gutter-repairs/ before writing</t>
         </is>
       </c>
     </row>
@@ -4540,15 +4540,15 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Gutter Fall and Bracket Spacing Explained</t>
+          <t>Gutter Brackets and Fall Explained | Manchester Gutters</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Gutter Fall and Bracket Spacing Explained</t>
+          <t>Gutter Brackets and Fall Explained</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4578,14 +4578,14 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>840 UK searches a month across 5 searches (fall for guttering 480; guttering fall per metre 140; how far apart should gutter brackets be 110; how many gutter brackets per meter 70). Overlap test against /gutter-replacement/ before writing</t>
+          <t>2,480 UK searches a month across 20 searches (gutter brackets rise and fall 590; fall for guttering 480; types of gutter brackets 170; guttering fall per metre 140). Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>/blog/rogue-roofers/</t>
+          <t>/blog/how-to-replace-guttering/</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4608,15 +4608,15 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>How to Spot a Rogue Roofer and Hire Safely</t>
+          <t>How to Replace Guttering Step by Step | Manchester Gutters</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>How to Spot a Rogue Roofer and Hire Safely</t>
+          <t>How to Replace Guttering Step by Step</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4646,23 +4646,23 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>280 UK searches a month across 6 searches (roofing scams 90; cowboy roofers 90; rogue roofers 40; roofing scams uk 30). Folded in as sections: how to complain about a builder. Sister site: Munster "Irish roofer scams": 72 clicks</t>
+          <t>1,290 UK searches a month across 14 searches (how to replace guttering 480; how to fit guttering 210; how to fix guttering 170; how to cut guttering 170). Folded in as sections: tools for fitting guttering, gutter installation mistakes. Sister site: Munster step-by-step installation guide: 68 clicks. Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/blog/are-gutter-guards-worth-it/</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Blog index</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
@@ -4671,62 +4671,66 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Guttering Guides and Costs | Manchester Gutters</t>
+          <t>Gutter Guards, Are They Worth Fitting? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Guttering guides</t>
+          <t>Gutter Guards, Are They Worth Fitting?</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>200-400</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Groups by topic; 20 cards then pages</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>nav</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>every article</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>CollectionPage, BreadcrumbList</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>350 UK searches a month across 6 searches (best gutter guards 170; cost of gutter guards 50; are gutter guards worth it 40; what gutter guard is best 30). Overlap test against /gutter-replacement/ before writing</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>/reviews/</t>
+          <t>/blog/rogue-roofers/</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Article: pillar</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
@@ -4735,58 +4739,62 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch, after the overlap test</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>How to Spot a Rogue Roofer and Hire Safely</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>How to Spot a Rogue Roofer and Hire Safely</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>1,000-1,800</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>blog index; hub guide cards</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>BlogPosting, BreadcrumbList, FAQPage</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>280 UK searches a month across 6 searches (roofing scams 90; cowboy roofers 90; rogue roofers 40; roofing scams uk 30). Folded in as sections: how to complain about a builder. Sister site: Munster "Irish roofer scams": 72 clicks</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>/case-studies/</t>
+          <t>/blog/</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Blog index</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4799,45 +4807,45 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Case Studies | Manchester Gutters</t>
+          <t>Guttering Guides and Costs | Manchester Gutters</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Case Studies</t>
+          <t>Guttering guides</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>200-400</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Groups by topic; 20 cards then pages</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>nav</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>every article</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+          <t>CollectionPage, BreadcrumbList</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr"/>
@@ -4845,7 +4853,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>/price-guide/</t>
+          <t>/reviews/</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4868,15 +4876,15 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide | Manchester Gutters</t>
+          <t>Manchester Gutters Reviews and Ratings</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide</t>
+          <t>Manchester Gutters Reviews and Ratings</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4909,7 +4917,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>/gallery/</t>
+          <t>/case-studies/</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4932,15 +4940,15 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs | Manchester Gutters</t>
+          <t>Case Studies | Manchester Gutters</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs</t>
+          <t>Case Studies</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4973,12 +4981,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>/about/</t>
+          <t>/price-guide/</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Proof</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4991,45 +4999,45 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>When records exist</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters | Local Guttering Team</t>
+          <t>Guttering Price Guide | Manchester Gutters</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters</t>
+          <t>Guttering Price Guide</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>600-1,200</t>
+          <t>as records allow</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Named people, credentials table, contact by area, map after consent</t>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>nav; footer; towns and services (1 in prose)</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>issuers (Google profile, memberships)</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>AboutPage / ContactPage + Organization reference</t>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr"/>
@@ -5037,12 +5045,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>/contact/</t>
+          <t>/gallery/</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Proof</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -5055,45 +5063,45 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>When records exist</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
+          <t>Gallery of Recent Jobs | Manchester Gutters</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters</t>
+          <t>Gallery of Recent Jobs</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>600-1,200</t>
+          <t>as records allow</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Named people, credentials table, contact by area, map after consent</t>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>nav; footer; towns and services (1 in prose)</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>issuers (Google profile, memberships)</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>AboutPage / ContactPage + Organization reference</t>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr"/>
@@ -5101,12 +5109,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>/privacy-policy/</t>
+          <t>/about/</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -5124,25 +5132,25 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy | Manchester Gutters</t>
+          <t>About Manchester Gutters | Local Guttering Team</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy</t>
+          <t>About Manchester Gutters</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>as needed</t>
+          <t>600-1,200</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>What the site really does</t>
+          <t>Named people, credentials table, contact by area, map after consent</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5157,7 +5165,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>WebPage</t>
+          <t>AboutPage / ContactPage + Organization reference</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
@@ -5165,12 +5173,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>/cookie-policy/</t>
+          <t>/contact/</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -5188,25 +5196,25 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Cookie Policy | Manchester Gutters</t>
+          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Contact Manchester Gutters</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>as needed</t>
+          <t>600-1,200</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>What the site really does</t>
+          <t>Named people, credentials table, contact by area, map after consent</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5221,7 +5229,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>WebPage</t>
+          <t>AboutPage / ContactPage + Organization reference</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr"/>
@@ -5229,22 +5237,20 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>/404</t>
+          <t>/privacy-policy/</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5254,67 +5260,61 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Privacy Policy | Manchester Gutters</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Privacy Policy</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>as needed</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>What the site really does</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>nav; footer</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>nav only</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>served with HTTP status 404</t>
-        </is>
-      </c>
+          <t>WebPage</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>/sitemap.xml</t>
+          <t>/cookie-policy/</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Non-indexable</t>
+          <t>Indexable</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5324,52 +5324,48 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Cookie Policy | Manchester Gutters</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>as needed</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>What the site really does</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>nav; footer</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>nav only</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>indexable pages only; real lastmod dates</t>
-        </is>
-      </c>
+          <t>WebPage</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>/robots.txt</t>
+          <t>/404</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5432,14 +5428,14 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>allows the AI search crawlers; points to the sitemap</t>
+          <t>served with HTTP status 404</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>/llms.txt</t>
+          <t>/sitemap.xml</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5502,12 +5498,152 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
+          <t>indexable pages only; real lastmod dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>/robots.txt</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>allows the AI search crawlers; points to the sitemap</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>/llms.txt</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
           <t>public facts only, from the facts file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N75"/>
+  <autoFilter ref="A1:N77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
+++ b/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal HTML'!$A$1:$N$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>4,270 UK searches a month across 35 searches (gutter replacement cost 1300; how much to replace guttering 390; new gutters price 320; how much do gutters cost 170). Folded in as sections: how long does guttering last, guttering building regulations. Sister site: Munster "how much to replace gutters" (234 impressions, position 5). Overlap test against /gutter-replacement/ before writing</t>
+          <t>4,270 UK searches a month across 35 searches (gutter replacement cost 1300; how much to replace guttering 390; new gutters price 320; how much do gutters cost 170). Folded in as sections: how long does guttering last, guttering building regulations. Sister site: Munster "how much to replace gutters" (234 impressions, position 5). Overlap test passed: 20% vs "gutter replacement manchester" (/gutter-replacement/)</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2,590 UK searches a month across 28 searches (cost of fascia and soffit replacement 590; soffit and fascia prices 390; fascia replacement cost 210; fascia board replacement cost 210). Folded in as sections: fascia capping vs replacement. Sister site: Munster fascia and soffit cost article: 57 clicks. Overlap test against /fascias-and-soffits/ before writing</t>
+          <t>3,550 UK searches a month across 38 searches (cost of fascia and soffit replacement 590; soffit and fascia prices 390; gutter fascia and soffit replacement cost 320; gutter and fascia replacement cost 320). Folded in as sections: fascia capping vs replacement, gutters, fascias and soffits replaced together (from roofline-replacement-cost, 90% overlap). Sister site: Munster fascia and soffit cost article: 57 clicks. Overlap test passed: 10% vs "fascias and soffits manchester" (/fascias-and-soffits/); 40% vs "gutter replacement cost" (/blog/gutter-replacement-cost/)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>/blog/roofline-replacement-cost/</t>
+          <t>/blog/gutter-repair-cost/</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3855,20 +3855,20 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Cost of New Gutters, Fascias and Soffits</t>
+          <t>How Much Do Gutter Repairs Cost? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Cost of New Gutters, Fascias and Soffits</t>
+          <t>How Much Do Gutter Repairs Cost?</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3898,14 +3898,14 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>960 UK searches a month across 10 searches (gutter fascia and soffit replacement cost 320; gutter and fascia replacement cost 320; fascias and guttering cost 70; new gutter and fascia cost 50). Overlap test against /fascias-and-soffits/ and /gutter-replacement/ before writing</t>
+          <t>640 UK searches a month across 9 searches (gutter repair cost 390; gutter leak repair cost 90; how much to repair gutters 50; leaking gutter repair cost 30). Sister site: Munster "Average cost of gutter repairs": 33 clicks. Overlap test passed: 0% vs "gutter repairs manchester" (/gutter-repairs/)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-repair-cost/</t>
+          <t>/blog/concrete-finlock-gutters/</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3928,15 +3928,15 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>How Much Do Gutter Repairs Cost? | Manchester Gutters</t>
+          <t>Concrete Finlock Gutters, Repair or Replace</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>How Much Do Gutter Repairs Cost?</t>
+          <t>Concrete Finlock Gutters, Repair or Replace</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3966,14 +3966,14 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>640 UK searches a month across 9 searches (gutter repair cost 390; gutter leak repair cost 90; how much to repair gutters 50; leaking gutter repair cost 30). Sister site: Munster "Average cost of gutter repairs": 33 clicks. Overlap test against /gutter-repairs/ before writing</t>
+          <t>240 UK searches a month across 4 searches (concrete gutter replacement cost 70; concrete gutter repair 70; finlock gutter removal cost 50; finlock gutter repair 50). Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>/blog/concrete-finlock-gutters/</t>
+          <t>/blog/what-are-fascias-and-soffits/</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3991,20 +3991,20 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Concrete Finlock Gutters, Repair or Replace</t>
+          <t>What Are Fascias and Soffits on a House?</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Concrete Finlock Gutters, Repair or Replace</t>
+          <t>What Are Fascias and Soffits on a House?</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); three cost tables (by property type, additional costs, lifespan) from the client's records; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
+          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4034,14 +4034,14 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>240 UK searches a month across 4 searches (concrete gutter replacement cost 70; concrete gutter repair 70; finlock gutter removal cost 50; finlock gutter repair 50). Overlap test against /gutter-replacement/ before writing</t>
+          <t>4,120 UK searches a month across 19 searches (what are soffits and fascias 1300; what are fascias on a house 590; fascia vs soffit 320; what are soffits on a house 320). Overlap test passed: 0% vs "fascias and soffits manchester" (/fascias-and-soffits/)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>/blog/what-are-fascias-and-soffits/</t>
+          <t>/blog/leaking-gutter-joint/</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4059,20 +4059,20 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>What Are Fascias and Soffits on a House?</t>
+          <t>How to Fix a Leaking Gutter Joint | Manchester Gutters</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>What Are Fascias and Soffits on a House?</t>
+          <t>How to Fix a Leaking Gutter Joint</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -4102,14 +4102,14 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>4,120 UK searches a month across 19 searches (what are soffits and fascias 1300; what are fascias on a house 590; fascia vs soffit 320; what are soffits on a house 320). Overlap test against /fascias-and-soffits/ before writing</t>
+          <t>2,410 UK searches a month across 16 searches (gutter leaking at joint 1000; sealing gutter joints 390; how to fix a leaking gutter joint 260; fix leaking gutter joint 170). Overlap test passed: 30% vs "gutter leaking" (/blog/why-is-my-gutter-leaking/)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>/blog/leaking-gutter-joint/</t>
+          <t>/blog/why-is-my-gutter-leaking/</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -4127,20 +4127,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>How to Fix a Leaking Gutter Joint | Manchester Gutters</t>
+          <t>Why Is My Gutter Leaking and How to Fix It</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>How to Fix a Leaking Gutter Joint</t>
+          <t>Why Is My Gutter Leaking and How to Fix It</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>2,410 UK searches a month across 16 searches (gutter leaking at joint 1000; sealing gutter joints 390; how to fix a leaking gutter joint 260; fix leaking gutter joint 170). Overlap test against /gutter-repairs/ before writing</t>
+          <t>1,600 UK searches a month across 13 searches (gutter leaking 480; gutter leak repairs 480; how to fix a leaking gutter 210; sealing gutter leaks 140). Overlap test passed: 0% vs "gutter repairs manchester" (/gutter-repairs/)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>/blog/why-is-my-gutter-leaking/</t>
+          <t>/blog/blocked-downpipe/</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4200,15 +4200,15 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Why Is My Gutter Leaking and How to Fix It</t>
+          <t>Blocked or Leaking Downpipe? What to Do | Manchester Gutters</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Why Is My Gutter Leaking and How to Fix It</t>
+          <t>Blocked or Leaking Downpipe? What to Do</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,600 UK searches a month across 13 searches (gutter leaking 480; gutter leak repairs 480; how to fix a leaking gutter 210; sealing gutter leaks 140). Overlap test against /gutter-repairs/ before writing</t>
+          <t>990 UK searches a month across 11 searches (downpipe blocked 260; blocked downpipe from gutter 210; how to unblock a downpipe 110; downpipe leaking 90). Overlap test against /downpipes/ before writing</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>/blog/blocked-downpipe/</t>
+          <t>/blog/rotten-fascia-boards/</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4268,15 +4268,15 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Blocked or Leaking Downpipe? What to Do | Manchester Gutters</t>
+          <t>Rotten Fascia Boards, Repair or Replace?</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Blocked or Leaking Downpipe? What to Do</t>
+          <t>Rotten Fascia Boards, Repair or Replace?</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4306,14 +4306,14 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>990 UK searches a month across 11 searches (downpipe blocked 260; blocked downpipe from gutter 210; how to unblock a downpipe 110; downpipe leaking 90). Overlap test against /downpipes/ before writing</t>
+          <t>980 UK searches a month across 14 searches (fixing soffits and fascias 170; how to fit fascia boards 140; how to replace fascia and soffit 110; how to install fascia boards 90). Folded in as sections: signs fascia needs replacing. Overlap test against /fascias-and-soffits/ before writing</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>/blog/rotten-fascia-boards/</t>
+          <t>/blog/box-gutter-leaking/</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4336,15 +4336,15 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Rotten Fascia Boards, Repair or Replace?</t>
+          <t>Leaking Box Gutters and Conservatory Gutters</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Rotten Fascia Boards, Repair or Replace?</t>
+          <t>Leaking Box Gutters and Conservatory Gutters</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4374,14 +4374,14 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>980 UK searches a month across 14 searches (fixing soffits and fascias 170; how to fit fascia boards 140; how to replace fascia and soffit 110; how to install fascia boards 90). Folded in as sections: signs fascia needs replacing. Overlap test against /fascias-and-soffits/ before writing</t>
+          <t>380 UK searches a month across 5 searches (conservatory box gutter leaking 140; what are box gutters 90; fixing box gutters 70; box gutter sizes 50). Overlap test against /gutter-repairs/ before writing</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>/blog/box-gutter-leaking/</t>
+          <t>/blog/gutters-overflowing/</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4404,15 +4404,15 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Leaking Box Gutters and Conservatory Gutters</t>
+          <t>Why Are My Gutters Overflowing? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Leaking Box Gutters and Conservatory Gutters</t>
+          <t>Why Are My Gutters Overflowing?</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4442,14 +4442,14 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>380 UK searches a month across 5 searches (conservatory box gutter leaking 140; what are box gutters 90; fixing box gutters 70; box gutter sizes 50). Overlap test against /gutter-repairs/ before writing</t>
+          <t>340 UK searches a month across 3 searches (gutters overflowing 260; gutter overflowing in heavy rain 70; why are my gutters overflowing 10). Overlap test against /gutter-repairs/ before writing</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutters-overflowing/</t>
+          <t>/blog/gutter-fall-and-bracket-spacing/</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4472,15 +4472,15 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Why Are My Gutters Overflowing? | Manchester Gutters</t>
+          <t>Gutter Brackets and Fall Explained | Manchester Gutters</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Why Are My Gutters Overflowing?</t>
+          <t>Gutter Brackets and Fall Explained</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4510,14 +4510,14 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>340 UK searches a month across 3 searches (gutters overflowing 260; gutter overflowing in heavy rain 70; why are my gutters overflowing 10). Overlap test against /gutter-repairs/ before writing</t>
+          <t>2,480 UK searches a month across 20 searches (gutter brackets rise and fall 590; fall for guttering 480; types of gutter brackets 170; guttering fall per metre 140). Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>/blog/gutter-fall-and-bracket-spacing/</t>
+          <t>/blog/how-to-replace-guttering/</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4540,15 +4540,15 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Gutter Brackets and Fall Explained | Manchester Gutters</t>
+          <t>How to Replace Guttering Step by Step | Manchester Gutters</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Gutter Brackets and Fall Explained</t>
+          <t>How to Replace Guttering Step by Step</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4578,14 +4578,14 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>2,480 UK searches a month across 20 searches (gutter brackets rise and fall 590; fall for guttering 480; types of gutter brackets 170; guttering fall per metre 140). Overlap test against /gutter-replacement/ before writing</t>
+          <t>1,290 UK searches a month across 14 searches (how to replace guttering 480; how to fit guttering 210; how to fix guttering 170; how to cut guttering 170). Folded in as sections: tools for fitting guttering, gutter installation mistakes. Sister site: Munster step-by-step installation guide: 68 clicks. Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>/blog/how-to-replace-guttering/</t>
+          <t>/blog/are-gutter-guards-worth-it/</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4608,15 +4608,15 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>How to Replace Guttering Step by Step | Manchester Gutters</t>
+          <t>Gutter Guards, Are They Worth Fitting? | Manchester Gutters</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>How to Replace Guttering Step by Step</t>
+          <t>Gutter Guards, Are They Worth Fitting?</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4646,14 +4646,14 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>1,290 UK searches a month across 14 searches (how to replace guttering 480; how to fit guttering 210; how to fix guttering 170; how to cut guttering 170). Folded in as sections: tools for fitting guttering, gutter installation mistakes. Sister site: Munster step-by-step installation guide: 68 clicks. Overlap test against /gutter-replacement/ before writing</t>
+          <t>350 UK searches a month across 6 searches (best gutter guards 170; cost of gutter guards 50; are gutter guards worth it 40; what gutter guard is best 30). Overlap test against /gutter-replacement/ before writing</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>/blog/are-gutter-guards-worth-it/</t>
+          <t>/blog/rogue-roofers/</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4676,15 +4676,15 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Gutter Guards, Are They Worth Fitting? | Manchester Gutters</t>
+          <t>How to Spot a Rogue Roofer and Hire Safely</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Gutter Guards, Are They Worth Fitting?</t>
+          <t>How to Spot a Rogue Roofer and Hire Safely</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4714,23 +4714,23 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>350 UK searches a month across 6 searches (best gutter guards 170; cost of gutter guards 50; are gutter guards worth it 40; what gutter guard is best 30). Overlap test against /gutter-replacement/ before writing</t>
+          <t>280 UK searches a month across 6 searches (roofing scams 90; cowboy roofers 90; rogue roofers 40; roofing scams uk 30). Folded in as sections: how to complain about a builder. Sister site: Munster "Irish roofer scams": 72 clicks</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>/blog/rogue-roofers/</t>
+          <t>/blog/</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Article: pillar</t>
+          <t>Blog index</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
@@ -4739,62 +4739,58 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>How to Spot a Rogue Roofer and Hire Safely</t>
+          <t>Guttering Guides and Costs | Manchester Gutters</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>How to Spot a Rogue Roofer and Hire Safely</t>
+          <t>Guttering guides</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,000-1,800</t>
+          <t>200-400</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Breadcrumb + meta; photo; 40-60-word answer; at a glance bullets; contents list (H2 anchors); Read next; question H2s (60%+); comparison or step table; case/review/video if records; who to hire; guarantees; FAQ 10-12; sources and further reading; related cards; CTA + form</t>
+          <t>Groups by topic; 20 cards then pages</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>blog index; hub guide cards</t>
+          <t>nav</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>services (3-5 in prose); the place hub; Read next 3-4; primary sources</t>
+          <t>every article</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>BlogPosting, BreadcrumbList, FAQPage</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>280 UK searches a month across 6 searches (roofing scams 90; cowboy roofers 90; rogue roofers 40; roofing scams uk 30). Folded in as sections: how to complain about a builder. Sister site: Munster "Irish roofer scams": 72 clicks</t>
-        </is>
-      </c>
+          <t>CollectionPage, BreadcrumbList</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/reviews/</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Blog index</t>
+          <t>Proof</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4807,45 +4803,45 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>When records exist</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Guttering Guides and Costs | Manchester Gutters</t>
+          <t>Manchester Gutters Reviews and Ratings</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Guttering guides</t>
+          <t>Manchester Gutters Reviews and Ratings</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>200-400</t>
+          <t>as records allow</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Groups by topic; 20 cards then pages</t>
+          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>nav</t>
+          <t>nav; footer; towns and services (1 in prose)</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>every article</t>
+          <t>issuers (Google profile, memberships)</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>CollectionPage, BreadcrumbList</t>
+          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr"/>
@@ -4853,7 +4849,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>/reviews/</t>
+          <t>/case-studies/</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4876,15 +4872,15 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>Case Studies | Manchester Gutters</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Manchester Gutters Reviews and Ratings</t>
+          <t>Case Studies</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4917,7 +4913,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>/case-studies/</t>
+          <t>/price-guide/</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4940,15 +4936,15 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Case Studies | Manchester Gutters</t>
+          <t>Guttering Price Guide | Manchester Gutters</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Case Studies</t>
+          <t>Guttering Price Guide</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4981,7 +4977,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>/price-guide/</t>
+          <t>/gallery/</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5004,15 +5000,15 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide | Manchester Gutters</t>
+          <t>Gallery of Recent Jobs | Manchester Gutters</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Guttering Price Guide</t>
+          <t>Gallery of Recent Jobs</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -5045,12 +5041,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>/gallery/</t>
+          <t>/about/</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -5063,45 +5059,45 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>When records exist</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs | Manchester Gutters</t>
+          <t>About Manchester Gutters | Local Guttering Team</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Gallery of Recent Jobs</t>
+          <t>About Manchester Gutters</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>as records allow</t>
+          <t>600-1,200</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Records only (exact quotes, dated, with area; or case cards, photos, price tables); check-it-yourself links; CTA + form</t>
+          <t>Named people, credentials table, contact by area, map after consent</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>nav; footer; towns and services (1 in prose)</t>
+          <t>nav; footer</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>issuers (Google profile, memberships)</t>
+          <t>nav only</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Organization reference; Review/AggregateRating only where shown; ImageGallery</t>
+          <t>AboutPage / ContactPage + Organization reference</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr"/>
@@ -5109,7 +5105,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>/about/</t>
+          <t>/contact/</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5132,15 +5128,15 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters | Local Guttering Team</t>
+          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>About Manchester Gutters</t>
+          <t>Contact Manchester Gutters</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -5173,12 +5169,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>/contact/</t>
+          <t>/privacy-policy/</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -5196,25 +5192,25 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters | Free Guttering Quotes</t>
+          <t>Privacy Policy | Manchester Gutters</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Contact Manchester Gutters</t>
+          <t>Privacy Policy</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>600-1,200</t>
+          <t>as needed</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Named people, credentials table, contact by area, map after consent</t>
+          <t>What the site really does</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5229,7 +5225,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>AboutPage / ContactPage + Organization reference</t>
+          <t>WebPage</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr"/>
@@ -5237,7 +5233,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>/privacy-policy/</t>
+          <t>/cookie-policy/</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5260,15 +5256,15 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy | Manchester Gutters</t>
+          <t>Cookie Policy | Manchester Gutters</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -5301,71 +5297,77 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>/cookie-policy/</t>
+          <t>/404</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Non-indexable</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Indexable</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Cookie Policy | Manchester Gutters</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>34</v>
-      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>as needed</t>
+          <t>–</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>What the site really does</t>
+          <t>–</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>nav; footer</t>
+          <t>–</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>nav only</t>
+          <t>–</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>WebPage</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>served with HTTP status 404</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>/404</t>
+          <t>/sitemap.xml</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5428,14 +5430,14 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>served with HTTP status 404</t>
+          <t>indexable pages only; real lastmod dates</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>/sitemap.xml</t>
+          <t>/robots.txt</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5498,14 +5500,14 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>indexable pages only; real lastmod dates</t>
+          <t>allows the AI search crawlers; points to the sitemap</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>/robots.txt</t>
+          <t>/llms.txt</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5568,82 +5570,12 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>allows the AI search crawlers; points to the sitemap</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>/llms.txt</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Non-indexable</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
           <t>public facts only, from the facts file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N77"/>
+  <autoFilter ref="A1:N76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
+++ b/.claude/skills/site-content/assets/manchester-gutters-url-map.xlsx
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>240 UK searches a month across 4 searches (concrete gutter replacement cost 70; concrete gutter repair 70; finlock gutter removal cost 50; finlock gutter repair 50). Overlap test against /gutter-replacement/ before writing</t>
+          <t>240 UK searches a month across 4 searches (concrete gutter replacement cost 70; concrete gutter repair 70; finlock gutter removal cost 50; finlock gutter repair 50). Overlap test passed: 20% vs "gutter replacement manchester" (/gutter-replacement/); 40% vs "gutter replacement cost" (/blog/gutter-replacement-cost/)</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>990 UK searches a month across 11 searches (downpipe blocked 260; blocked downpipe from gutter 210; how to unblock a downpipe 110; downpipe leaking 90). Overlap test against /downpipes/ before writing</t>
+          <t>990 UK searches a month across 11 searches (downpipe blocked 260; blocked downpipe from gutter 210; how to unblock a downpipe 110; downpipe leaking 90). Overlap test passed: 0% vs "downpipe repairs manchester" (/downpipes/)</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>980 UK searches a month across 14 searches (fixing soffits and fascias 170; how to fit fascia boards 140; how to replace fascia and soffit 110; how to install fascia boards 90). Folded in as sections: signs fascia needs replacing. Overlap test against /fascias-and-soffits/ before writing</t>
+          <t>980 UK searches a month across 14 searches (fixing soffits and fascias 170; how to fit fascia boards 140; how to replace fascia and soffit 110; how to install fascia boards 90). Folded in as sections: signs fascia needs replacing. Overlap test passed: 10% vs "fascias and soffits manchester" (/fascias-and-soffits/); 10% vs "fascia and soffit replacement cost" (/blog/fascia-and-soffit-replacement-cost/)</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>380 UK searches a month across 5 searches (conservatory box gutter leaking 140; what are box gutters 90; fixing box gutters 70; box gutter sizes 50). Overlap test against /gutter-repairs/ before writing</t>
+          <t>380 UK searches a month across 5 searches (conservatory box gutter leaking 140; what are box gutters 90; fixing box gutters 70; box gutter sizes 50). Overlap test passed: 0% vs "gutter repairs manchester" (/gutter-repairs/); 10% vs "gutter leaking" (/blog/why-is-my-gutter-leaking/)</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>340 UK searches a month across 3 searches (gutters overflowing 260; gutter overflowing in heavy rain 70; why are my gutters overflowing 10). Overlap test against /gutter-repairs/ before writing</t>
+          <t>340 UK searches a month across 3 searches (gutters overflowing 260; gutter overflowing in heavy rain 70; why are my gutters overflowing 10). Overlap test passed: 0% vs "gutter repairs manchester" (/gutter-repairs/); 10% vs "gutter leaking" (/blog/why-is-my-gutter-leaking/)</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2,480 UK searches a month across 20 searches (gutter brackets rise and fall 590; fall for guttering 480; types of gutter brackets 170; guttering fall per metre 140). Overlap test against /gutter-replacement/ before writing</t>
+          <t>2,480 UK searches a month across 20 searches (gutter brackets rise and fall 590; fall for guttering 480; types of gutter brackets 170; guttering fall per metre 140). Overlap test passed: 0% vs "gutter replacement manchester" (/gutter-replacement/); 0% vs "how to replace guttering" (/blog/how-to-replace-guttering/)</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>1,290 UK searches a month across 14 searches (how to replace guttering 480; how to fit guttering 210; how to fix guttering 170; how to cut guttering 170). Folded in as sections: tools for fitting guttering, gutter installation mistakes. Sister site: Munster step-by-step installation guide: 68 clicks. Overlap test against /gutter-replacement/ before writing</t>
+          <t>1,290 UK searches a month across 14 searches (how to replace guttering 480; how to fit guttering 210; how to fix guttering 170; how to cut guttering 170). Folded in as sections: tools for fitting guttering, gutter installation mistakes. Sister site: Munster step-by-step installation guide: 68 clicks. Overlap test passed: 0% vs "gutter replacement manchester" (/gutter-replacement/); 0% vs "gutter replacement cost" (/blog/gutter-replacement-cost/)</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>350 UK searches a month across 6 searches (best gutter guards 170; cost of gutter guards 50; are gutter guards worth it 40; what gutter guard is best 30). Overlap test against /gutter-replacement/ before writing</t>
+          <t>350 UK searches a month across 6 searches (best gutter guards 170; cost of gutter guards 50; are gutter guards worth it 40; what gutter guard is best 30). Overlap test passed: 0% vs "gutter replacement manchester" (/gutter-replacement/)</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Launch, after the overlap test</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
